--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488120_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488120_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3114</v>
+        <v>6.6931</v>
       </c>
       <c r="E2" t="n">
-        <v>2.88</v>
+        <v>2.8405</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4314</v>
+        <v>3.8526</v>
       </c>
       <c r="G2" t="n">
         <v>3.7832</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0019</v>
+        <v>0.3836</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0696</v>
+        <v>-0.1091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.4927</v>
       </c>
       <c r="V2" t="n">
         <v>0.9405</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9539</v>
+        <v>5.0506</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6449</v>
+        <v>3.7697</v>
       </c>
       <c r="F3" t="n">
-        <v>1.309</v>
+        <v>1.2809</v>
       </c>
       <c r="G3" t="n">
         <v>3.6058</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5992</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.132</v>
+        <v>-0.0072</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6065</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1367</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.182</v>
+        <v>4.0084</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8743</v>
+        <v>2.8972</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3077</v>
+        <v>1.1112</v>
       </c>
       <c r="G4" t="n">
         <v>1.0842</v>
@@ -766,13 +766,13 @@
         <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0384</v>
+        <v>1.8648</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6829</v>
+        <v>0.7058</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3555</v>
+        <v>1.1589</v>
       </c>
       <c r="V4" t="n">
         <v>0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9294</v>
+        <v>3.0268</v>
       </c>
       <c r="E5" t="n">
-        <v>2.008</v>
+        <v>1.929</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9214</v>
+        <v>1.0978</v>
       </c>
       <c r="G5" t="n">
         <v>1.9132</v>
@@ -844,13 +844,13 @@
         <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8863</v>
+        <v>0.9837</v>
       </c>
       <c r="T5" t="n">
-        <v>0.18</v>
+        <v>0.101</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7063</v>
+        <v>0.8827</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2666</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.172</v>
+        <v>2.7188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9626</v>
+        <v>0.4533</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2094</v>
+        <v>2.2655</v>
       </c>
       <c r="G6" t="n">
         <v>1.166</v>
@@ -922,13 +922,13 @@
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3847</v>
+        <v>0.9315</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7967</v>
+        <v>0.2873</v>
       </c>
       <c r="U6" t="n">
-        <v>0.588</v>
+        <v>0.6441</v>
       </c>
       <c r="V6" t="n">
         <v>1.8107</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8135</v>
+        <v>2.4151</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5678</v>
+        <v>0.6722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2457</v>
+        <v>1.7429</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3492</v>
+        <v>0.8939</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1713</v>
+        <v>1.598</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1778</v>
+        <v>-0.704</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5221</v>
+        <v>1.3328</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3613</v>
+        <v>1.9238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1607</v>
+        <v>-0.591</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1729</v>
+        <v>-0.4388</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.19</v>
+        <v>-0.3258</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0171</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
         <v>-1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6537</v>
+        <v>1.5629</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4244</v>
+        <v>0.5021</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2292</v>
+        <v>1.0608</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>1.5441</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6036</v>
+        <v>1.8107</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3713</v>
+        <v>2.1579</v>
       </c>
       <c r="E8" t="n">
-        <v>0.853</v>
+        <v>0.6413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5183</v>
+        <v>1.5166</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8939</v>
+        <v>3.6357</v>
       </c>
       <c r="H8" t="n">
-        <v>1.598</v>
+        <v>1.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.704</v>
+        <v>2.5639</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3328</v>
+        <v>2.194</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9238</v>
+        <v>1.1299</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.591</v>
+        <v>1.0641</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4388</v>
+        <v>1.4417</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3258</v>
+        <v>-0.0581</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.113</v>
+        <v>1.4998</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5858</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>1.519</v>
+        <v>0.7204</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6829</v>
+        <v>-0.0531</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8361</v>
+        <v>0.7735</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5441</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8107</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8107</v>
+        <v>2.1347</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8107</v>
+        <v>1.9171</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.2176</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8107</v>
+        <v>2.3492</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.1713</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2053</v>
+        <v>0.1778</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8107</v>
+        <v>2.5221</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.3613</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2053</v>
+        <v>0.1607</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.1729</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.9749</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.7738</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2011</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5267</v>
+        <v>1.8107</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3751</v>
+        <v>1.8107</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1516</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6357</v>
+        <v>1.8107</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0718</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5639</v>
+        <v>1.2053</v>
       </c>
       <c r="J10" t="n">
-        <v>2.194</v>
+        <v>1.8107</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1299</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0641</v>
+        <v>1.2053</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4417</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0581</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4998</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0893</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3192</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0959</v>
+        <v>0.4749</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4779</v>
+        <v>0.9083</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5738</v>
+        <v>-0.4334</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0023</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2918</v>
+        <v>0.279</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2496</v>
+        <v>0.1808</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0422</v>
+        <v>0.0982</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.226</v>
+        <v>-0.5138</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8891</v>
+        <v>-2.3174</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6631</v>
+        <v>1.8035</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8379</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2405</v>
+        <v>0.4717</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7488</v>
+        <v>-0.177</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5083</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7552</v>
+        <v>-1.2739</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0239</v>
+        <v>-2.5146</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2688</v>
+        <v>1.2407</v>
       </c>
       <c r="G14" t="n">
         <v>-1.6074</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2309</v>
+        <v>0.7121</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2386</v>
+        <v>0.2708</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4694</v>
+        <v>0.4413</v>
       </c>
       <c r="V14" t="n">
         <v>1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.7292</v>
+        <v>-2.4559</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3887</v>
+        <v>-1.9189</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3404</v>
+        <v>-0.537</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5451</v>
@@ -1624,13 +1624,13 @@
         <v>0.1982</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.0893</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.301</v>
+        <v>0.1689</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1169</v>
+        <v>0.9204</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2071</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>26.77260000000001</v>
+        <v>27.7554</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6606</v>
+        <v>12.5964</v>
       </c>
       <c r="F16" t="n">
-        <v>15.1122</v>
+        <v>15.1589</v>
       </c>
       <c r="G16" t="n">
         <v>17.75719999999999</v>
@@ -1702,22 +1702,22 @@
         <v>11.8933</v>
       </c>
       <c r="S16" t="n">
-        <v>10.5904</v>
+        <v>11.5731</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7081</v>
+        <v>2.6441</v>
       </c>
       <c r="U16" t="n">
-        <v>8.882100000000001</v>
+        <v>8.928900000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.4073999999999995</v>
       </c>
       <c r="W16" t="n">
-        <v>7.368599999999999</v>
+        <v>7.368600000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.9611</v>
+        <v>-6.961100000000002</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2633</v>
+        <v>1.3149</v>
       </c>
       <c r="E17" t="n">
         <v>-0.6593</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9226</v>
+        <v>1.9742</v>
       </c>
       <c r="G17" t="n">
         <v>-2.4911</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8512</v>
+        <v>-1.7996</v>
       </c>
       <c r="T17" t="n">
         <v>-1.7471</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1041</v>
+        <v>-0.0525</v>
       </c>
       <c r="V17" t="n">
         <v>3.4252</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2622</v>
+        <v>0.4098</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9979</v>
+        <v>1.2017</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7357</v>
+        <v>-0.7919</v>
       </c>
       <c r="G19" t="n">
         <v>0.1125</v>
@@ -1936,13 +1936,13 @@
         <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2467</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0653</v>
+        <v>0.0091</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2919</v>
+        <v>-0.2983</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4487</v>
+        <v>-0.479</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1568</v>
+        <v>0.1807</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6174</v>
+        <v>0.6283</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6585</v>
+        <v>0.4906</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.2759</v>
+        <v>0.1376</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4435</v>
+        <v>1.9986</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1123</v>
+        <v>1.3519</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.5558</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1739</v>
+        <v>-1.3704</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4538</v>
+        <v>-0.8613</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7201</v>
+        <v>-0.5091</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8884</v>
+        <v>-1.5124</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2369</v>
+        <v>-1.4865</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3485</v>
+        <v>-0.0259</v>
       </c>
       <c r="V20" t="n">
-        <v>3.2139</v>
+        <v>-0.6036</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2139</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4341</v>
+        <v>-0.335</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.479</v>
+        <v>-0.3469</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0448</v>
+        <v>0.0119</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6283</v>
+        <v>-2.6174</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4906</v>
+        <v>1.6585</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1376</v>
+        <v>-4.2759</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9986</v>
+        <v>-0.4435</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3519</v>
+        <v>2.1123</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6467000000000001</v>
+        <v>-2.5558</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3704</v>
+        <v>-2.1739</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8613</v>
+        <v>-0.4538</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5091</v>
+        <v>-1.7201</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6482</v>
+        <v>-0.9315</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4865</v>
+        <v>-1.135</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1617</v>
+        <v>0.2036</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6036</v>
+        <v>3.2139</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.2139</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3593</v>
+        <v>-1.3873</v>
       </c>
       <c r="E22" t="n">
         <v>0.4202</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7794</v>
+        <v>-1.8075</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8053</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2169</v>
+        <v>-0.245</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3744</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V22" t="n">
         <v>-0.337</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1442</v>
+        <v>-3.0424</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0406</v>
+        <v>-0.9387</v>
       </c>
       <c r="F23" t="n">
         <v>-2.1036</v>
@@ -2248,10 +2248,10 @@
         <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6057</v>
+        <v>-0.5038</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1689</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1895</v>
+        <v>-3.6015</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3914</v>
+        <v>-2.7989</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.798</v>
+        <v>-0.8026</v>
       </c>
       <c r="G24" t="n">
         <v>-0.739</v>
@@ -2326,13 +2326,13 @@
         <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0957</v>
+        <v>-1.5078</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8184</v>
+        <v>-1.2259</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2773</v>
+        <v>-0.2819</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1476</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9132</v>
+        <v>-4.1907</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5497</v>
+        <v>-1.8553</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3636</v>
+        <v>-2.3355</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6853</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0298</v>
+        <v>-0.2478</v>
       </c>
       <c r="T25" t="n">
-        <v>0.191</v>
+        <v>-0.1146</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1612</v>
+        <v>-0.1332</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2666</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5286</v>
+        <v>-4.2172</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3048</v>
+        <v>-2.1011</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2238</v>
+        <v>-2.1161</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5591</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7713</v>
+        <v>-0.4598</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5505</v>
+        <v>-0.3468</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2207</v>
+        <v>-0.113</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6036</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.2562</v>
+        <v>-5.9297</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.984</v>
+        <v>-4.8821</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2722</v>
+        <v>-1.0476</v>
       </c>
       <c r="G27" t="n">
         <v>-3.9781</v>
@@ -2560,13 +2560,13 @@
         <v>1.3876</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0799</v>
+        <v>-0.7534</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6753</v>
+        <v>-0.5735</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4046</v>
+        <v>-0.18</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6036</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.3891</v>
+        <v>-6.0241</v>
       </c>
       <c r="E28" t="n">
         <v>-3.8808</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.5084</v>
+        <v>-2.1434</v>
       </c>
       <c r="G28" t="n">
         <v>-3.0255</v>
@@ -2638,13 +2638,13 @@
         <v>1.3876</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.216</v>
+        <v>-1.851</v>
       </c>
       <c r="T28" t="n">
         <v>-1.4351</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.7809</v>
+        <v>-0.4158</v>
       </c>
       <c r="V28" t="n">
         <v>-1.5441</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-26.7726</v>
+        <v>-26.0935</v>
       </c>
       <c r="E29" t="n">
         <v>-15.1122</v>
       </c>
       <c r="F29" t="n">
-        <v>-11.6605</v>
+        <v>-10.9814</v>
       </c>
       <c r="G29" t="n">
         <v>-17.7571</v>
@@ -2692,7 +2692,7 @@
         <v>-1.2977</v>
       </c>
       <c r="K29" t="n">
-        <v>1.589999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="L29" t="n">
         <v>-2.8875</v>
@@ -2716,13 +2716,13 @@
         <v>13.8757</v>
       </c>
       <c r="S29" t="n">
-        <v>-10.5902</v>
+        <v>-9.911199999999997</v>
       </c>
       <c r="T29" t="n">
-        <v>-8.882000000000001</v>
+        <v>-8.882</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.7082</v>
+        <v>-1.0291</v>
       </c>
       <c r="V29" t="n">
         <v>-0.4075000000000009</v>
@@ -2731,7 +2731,7 @@
         <v>6.961</v>
       </c>
       <c r="X29" t="n">
-        <v>-7.368700000000001</v>
+        <v>-7.3687</v>
       </c>
     </row>
   </sheetData>
